--- a/M_tacker/sample_2.xlsx
+++ b/M_tacker/sample_2.xlsx
@@ -19,10 +19,10 @@
     <t>tags</t>
   </si>
   <si>
+    <t>department</t>
+  </si>
+  <si>
     <t>user</t>
-  </si>
-  <si>
-    <t>department</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -51,13 +51,25 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,7 +80,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -80,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -88,7 +107,16 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
@@ -396,19 +424,19 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -416,44 +444,44 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4">
         <v>232</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4">
         <v>1215</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
         <v>1367</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
